--- a/inst/extdata/north_dakota_criteria_crosswalk.xlsx
+++ b/inst/extdata/north_dakota_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/k_salkgundersen_tetratech_com/Documents/EPA/R8_AssessmentTool/5_Work/Crosswalks/individual_criteria_crosswalks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{C61AC19D-9327-4129-BEDE-73F69395A6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B61FE58-7795-4241-802A-ABA4E428E29B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAF4E98-0AFF-4481-BB14-569D81D84F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="129">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -249,9 +249,6 @@
     </r>
   </si>
   <si>
-    <t>Ammonia, as N</t>
-  </si>
-  <si>
     <t>AMMONIA</t>
   </si>
   <si>
@@ -339,9 +336,6 @@
     <t>Class II and Class III</t>
   </si>
   <si>
-    <t>Chlorine Residual</t>
-  </si>
-  <si>
     <t>CHLORINE, TOTAL RESIDUAL</t>
   </si>
   <si>
@@ -354,15 +348,9 @@
     <t>CYLINDROSPERMOPSIN</t>
   </si>
   <si>
-    <t>Microcystin</t>
-  </si>
-  <si>
     <t>MICROCYSTIN</t>
   </si>
   <si>
-    <t>Oxygen</t>
-  </si>
-  <si>
     <t>DISSOLVED OXYGEN (DO)</t>
   </si>
   <si>
@@ -372,21 +360,12 @@
     <t>Percent of samples not meeting</t>
   </si>
   <si>
-    <t>Nitrate as N3</t>
-  </si>
-  <si>
     <t>NITRATE</t>
   </si>
   <si>
-    <t>Nitrite as N</t>
-  </si>
-  <si>
     <t>NITRITE</t>
   </si>
   <si>
-    <t>E. coli</t>
-  </si>
-  <si>
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
@@ -414,9 +393,6 @@
     <t>arithmetic extremes</t>
   </si>
   <si>
-    <t>Phenols</t>
-  </si>
-  <si>
     <t>PHENOLS</t>
   </si>
   <si>
@@ -459,13 +435,34 @@
     <t>Maximum increase shall not be greater than 5 deg F above natural background conditions</t>
   </si>
   <si>
-    <t>Radium-226 and Radium-228</t>
-  </si>
-  <si>
     <t>RADIUM-226/228</t>
   </si>
   <si>
     <t>pCi/L</t>
+  </si>
+  <si>
+    <t>NITROGEN, AMMONIA</t>
+  </si>
+  <si>
+    <t>CHLORINE, RESIDUAL (CHLORINE DEMAND)</t>
+  </si>
+  <si>
+    <t>CYANOBACTERIA HEPATOTOXIC MICROCYSTINS</t>
+  </si>
+  <si>
+    <t>DISSOLVED OXYGEN</t>
+  </si>
+  <si>
+    <t>NITROGEN, NITRITE</t>
+  </si>
+  <si>
+    <t>ESCHERICHIA COLI (E. COLI)</t>
+  </si>
+  <si>
+    <t>PHENOL</t>
+  </si>
+  <si>
+    <t>RADIUM</t>
   </si>
 </sst>
 </file>
@@ -882,13 +879,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D75899-4D8D-4FC8-9793-6F1E23FF217F}">
   <dimension ref="A1:AQ56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1017,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1090,7 +1088,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1163,22 +1161,22 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
@@ -1191,27 +1189,27 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="Q4" s="5">
-        <v>1</v>
-      </c>
-      <c r="R4" s="5" t="s">
+      <c r="S4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="T4" s="5">
+        <v>1</v>
+      </c>
+      <c r="U4" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="T4" s="5">
-        <v>1</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -1223,13 +1221,13 @@
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
       <c r="AE4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="AF4" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="AG4" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
@@ -1238,22 +1236,22 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
@@ -1266,27 +1264,27 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5" t="s">
+      <c r="S5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="T5" s="5">
+        <v>1</v>
+      </c>
+      <c r="U5" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="T5" s="5">
-        <v>1</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
@@ -1298,13 +1296,13 @@
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
       <c r="AE5" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AF5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG5" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="AG5" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
@@ -1313,22 +1311,22 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
@@ -1341,12 +1339,12 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q6" s="5">
         <v>30</v>
@@ -1355,13 +1353,13 @@
         <v>52</v>
       </c>
       <c r="S6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6" s="5">
+        <v>1</v>
+      </c>
+      <c r="U6" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="T6" s="5">
-        <v>1</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
@@ -1373,13 +1371,13 @@
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
@@ -1388,22 +1386,22 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
@@ -1416,12 +1414,12 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="5">
         <v>4</v>
@@ -1430,7 +1428,7 @@
         <v>52</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T7" s="5">
         <v>1</v>
@@ -1448,13 +1446,13 @@
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
       <c r="AE7" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AG7" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
@@ -1463,22 +1461,22 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -1488,7 +1486,7 @@
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>50</v>
@@ -1534,22 +1532,22 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -1559,7 +1557,7 @@
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>50</v>
@@ -1605,22 +1603,22 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="F10" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -1638,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q10" s="5">
         <v>1</v>
@@ -1647,7 +1645,7 @@
         <v>52</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T10" s="5">
         <v>1</v>
@@ -1674,22 +1672,22 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -1707,7 +1705,7 @@
         <v>0.75</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q11" s="5">
         <v>30</v>
@@ -1716,7 +1714,7 @@
         <v>52</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T11" s="5">
         <v>1</v>
@@ -1743,22 +1741,22 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -1776,7 +1774,7 @@
         <v>0.75</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q12" s="5">
         <v>30</v>
@@ -1785,7 +1783,7 @@
         <v>52</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T12" s="5">
         <v>1</v>
@@ -1812,22 +1810,22 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="F13" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -1845,7 +1843,7 @@
         <v>0.75</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="5">
         <v>30</v>
@@ -1854,7 +1852,7 @@
         <v>52</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T13" s="5">
         <v>1</v>
@@ -1881,22 +1879,22 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -1906,7 +1904,7 @@
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>50</v>
@@ -1916,7 +1914,7 @@
         <v>100</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="5">
         <v>30</v>
@@ -1925,7 +1923,7 @@
         <v>52</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T14" s="5">
         <v>1</v>
@@ -1952,22 +1950,22 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -1977,7 +1975,7 @@
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>50</v>
@@ -1987,7 +1985,7 @@
         <v>175</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q15" s="5">
         <v>30</v>
@@ -1996,7 +1994,7 @@
         <v>52</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T15" s="5">
         <v>1</v>
@@ -2023,22 +2021,22 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -2048,7 +2046,7 @@
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>50</v>
@@ -2058,7 +2056,7 @@
         <v>250</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q16" s="5">
         <v>30</v>
@@ -2067,7 +2065,7 @@
         <v>52</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T16" s="5">
         <v>1</v>
@@ -2094,22 +2092,22 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F17" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -2119,7 +2117,7 @@
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>50</v>
@@ -2129,7 +2127,7 @@
         <v>100</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q17" s="5">
         <v>30</v>
@@ -2138,7 +2136,7 @@
         <v>52</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T17" s="5">
         <v>1</v>
@@ -2165,22 +2163,22 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F18" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -2190,7 +2188,7 @@
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M18" s="5" t="s">
         <v>50</v>
@@ -2200,7 +2198,7 @@
         <v>175</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="5">
         <v>30</v>
@@ -2209,7 +2207,7 @@
         <v>52</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T18" s="5">
         <v>1</v>
@@ -2236,22 +2234,22 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F19" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -2261,7 +2259,7 @@
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>50</v>
@@ -2271,7 +2269,7 @@
         <v>250</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q19" s="5">
         <v>30</v>
@@ -2280,7 +2278,7 @@
         <v>52</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T19" s="5">
         <v>1</v>
@@ -2307,22 +2305,22 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -2332,7 +2330,7 @@
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M20" s="5" t="s">
         <v>50</v>
@@ -2342,7 +2340,7 @@
         <v>100</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="5">
         <v>30</v>
@@ -2351,7 +2349,7 @@
         <v>52</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T20" s="5">
         <v>1</v>
@@ -2378,22 +2376,22 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F21" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -2403,7 +2401,7 @@
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>50</v>
@@ -2413,7 +2411,7 @@
         <v>175</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q21" s="5">
         <v>30</v>
@@ -2422,7 +2420,7 @@
         <v>52</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T21" s="5">
         <v>1</v>
@@ -2449,22 +2447,22 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F22" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -2474,7 +2472,7 @@
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>50</v>
@@ -2484,7 +2482,7 @@
         <v>250</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q22" s="5">
         <v>30</v>
@@ -2493,7 +2491,7 @@
         <v>52</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T22" s="5">
         <v>1</v>
@@ -2520,22 +2518,22 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F23" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -2545,7 +2543,7 @@
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M23" s="5" t="s">
         <v>50</v>
@@ -2555,7 +2553,7 @@
         <v>100</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q23" s="5">
         <v>30</v>
@@ -2564,7 +2562,7 @@
         <v>52</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T23" s="5">
         <v>1</v>
@@ -2591,22 +2589,22 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F24" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -2616,7 +2614,7 @@
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>50</v>
@@ -2626,7 +2624,7 @@
         <v>175</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q24" s="5">
         <v>30</v>
@@ -2635,7 +2633,7 @@
         <v>52</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T24" s="5">
         <v>1</v>
@@ -2662,22 +2660,22 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
     </row>
-    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F25" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -2687,7 +2685,7 @@
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>50</v>
@@ -2697,7 +2695,7 @@
         <v>250</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q25" s="5">
         <v>30</v>
@@ -2706,7 +2704,7 @@
         <v>52</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T25" s="5">
         <v>1</v>
@@ -2733,22 +2731,22 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
     </row>
-    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F26" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -2758,7 +2756,7 @@
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>50</v>
@@ -2768,7 +2766,7 @@
         <v>100</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q26" s="5">
         <v>30</v>
@@ -2777,7 +2775,7 @@
         <v>52</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T26" s="5">
         <v>1</v>
@@ -2804,22 +2802,22 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
     </row>
-    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F27" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -2829,7 +2827,7 @@
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>50</v>
@@ -2839,7 +2837,7 @@
         <v>175</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q27" s="5">
         <v>30</v>
@@ -2848,7 +2846,7 @@
         <v>52</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T27" s="5">
         <v>1</v>
@@ -2875,22 +2873,22 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
     </row>
-    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="F28" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -2900,7 +2898,7 @@
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>50</v>
@@ -2910,7 +2908,7 @@
         <v>250</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q28" s="5">
         <v>30</v>
@@ -2919,7 +2917,7 @@
         <v>52</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T28" s="5">
         <v>1</v>
@@ -2946,22 +2944,22 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
@@ -2981,7 +2979,7 @@
         <v>1.9E-2</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q29" s="5">
         <v>1</v>
@@ -2990,7 +2988,7 @@
         <v>52</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T29" s="5">
         <v>1</v>
@@ -3017,22 +3015,22 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
@@ -3052,7 +3050,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q30" s="5">
         <v>30</v>
@@ -3061,7 +3059,7 @@
         <v>52</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T30" s="5">
         <v>1</v>
@@ -3088,19 +3086,19 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -3155,19 +3153,19 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D32" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -3222,19 +3220,19 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>47</v>
@@ -3255,7 +3253,7 @@
       </c>
       <c r="O33" s="5"/>
       <c r="P33" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q33" s="5">
         <v>1</v>
@@ -3264,13 +3262,13 @@
         <v>52</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="T33" s="5">
         <v>10</v>
       </c>
       <c r="U33" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="V33" s="5"/>
       <c r="W33" s="5"/>
@@ -3291,19 +3289,19 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -3322,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q34" s="5">
         <v>1</v>
@@ -3337,7 +3335,7 @@
         <v>10</v>
       </c>
       <c r="U34" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="V34" s="5"/>
       <c r="W34" s="5"/>
@@ -3358,19 +3356,19 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -3389,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q35" s="5">
         <v>1</v>
@@ -3404,7 +3402,7 @@
         <v>10</v>
       </c>
       <c r="U35" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="V35" s="5"/>
       <c r="W35" s="5"/>
@@ -3425,19 +3423,19 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -3456,7 +3454,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q36" s="5">
         <v>1</v>
@@ -3492,19 +3490,19 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -3523,7 +3521,7 @@
         <v>126</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q37" s="5">
         <v>30</v>
@@ -3532,19 +3530,19 @@
         <v>52</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="T37" s="5">
         <v>10</v>
       </c>
       <c r="U37" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="V37" s="5"/>
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
       <c r="Y37" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="Z37" s="5"/>
       <c r="AA37" s="5"/>
@@ -3561,19 +3559,19 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -3592,7 +3590,7 @@
         <v>409</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q38" s="5">
         <v>30</v>
@@ -3607,13 +3605,13 @@
         <v>10</v>
       </c>
       <c r="U38" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
       <c r="Y38" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="Z38" s="5"/>
       <c r="AA38" s="5"/>
@@ -3630,19 +3628,19 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
     </row>
-    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -3653,7 +3651,7 @@
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>50</v>
@@ -3665,7 +3663,7 @@
         <v>9</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="Q39" s="5">
         <v>1</v>
@@ -3674,7 +3672,7 @@
         <v>52</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="T39" s="5">
         <v>1</v>
@@ -3701,19 +3699,19 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -3724,7 +3722,7 @@
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>50</v>
@@ -3736,7 +3734,7 @@
         <v>9</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="Q40" s="5">
         <v>1</v>
@@ -3745,7 +3743,7 @@
         <v>52</v>
       </c>
       <c r="S40" s="5" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="T40" s="5">
         <v>1</v>
@@ -3772,19 +3770,19 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -3795,7 +3793,7 @@
       </c>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>50</v>
@@ -3807,7 +3805,7 @@
         <v>9</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="Q41" s="5">
         <v>1</v>
@@ -3816,7 +3814,7 @@
         <v>52</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="T41" s="5">
         <v>1</v>
@@ -3843,22 +3841,22 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -3876,7 +3874,7 @@
         <v>0.3</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q42" s="5">
         <v>1</v>
@@ -3885,7 +3883,7 @@
         <v>52</v>
       </c>
       <c r="S42" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T42" s="5">
         <v>1</v>
@@ -3903,7 +3901,7 @@
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="AF42" s="5"/>
       <c r="AG42" s="5"/>
@@ -3914,19 +3912,19 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -3937,7 +3935,7 @@
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>50</v>
@@ -3947,7 +3945,7 @@
         <v>50</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q43" s="5">
         <v>1</v>
@@ -3974,7 +3972,7 @@
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AF43" s="5"/>
       <c r="AG43" s="5"/>
@@ -3985,19 +3983,19 @@
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -4008,7 +4006,7 @@
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>50</v>
@@ -4018,7 +4016,7 @@
         <v>60</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q44" s="5">
         <v>1</v>
@@ -4045,7 +4043,7 @@
       <c r="AC44" s="5"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AF44" s="5"/>
       <c r="AG44" s="5"/>
@@ -4056,19 +4054,19 @@
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -4079,7 +4077,7 @@
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>50</v>
@@ -4089,7 +4087,7 @@
         <v>50</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q45" s="5">
         <v>1</v>
@@ -4116,7 +4114,7 @@
       <c r="AC45" s="5"/>
       <c r="AD45" s="5"/>
       <c r="AE45" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AF45" s="5"/>
       <c r="AG45" s="5"/>
@@ -4127,19 +4125,19 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -4150,7 +4148,7 @@
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>50</v>
@@ -4160,7 +4158,7 @@
         <v>60</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q46" s="5">
         <v>1</v>
@@ -4187,7 +4185,7 @@
       <c r="AC46" s="5"/>
       <c r="AD46" s="5"/>
       <c r="AE46" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AF46" s="5"/>
       <c r="AG46" s="5"/>
@@ -4198,19 +4196,19 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -4221,7 +4219,7 @@
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>50</v>
@@ -4231,7 +4229,7 @@
         <v>50</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q47" s="5">
         <v>1</v>
@@ -4258,7 +4256,7 @@
       <c r="AC47" s="5"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AF47" s="5"/>
       <c r="AG47" s="5"/>
@@ -4269,19 +4267,19 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -4292,7 +4290,7 @@
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>50</v>
@@ -4302,7 +4300,7 @@
         <v>60</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q48" s="5">
         <v>1</v>
@@ -4329,7 +4327,7 @@
       <c r="AC48" s="5"/>
       <c r="AD48" s="5"/>
       <c r="AE48" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AF48" s="5"/>
       <c r="AG48" s="5"/>
@@ -4340,19 +4338,19 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -4363,7 +4361,7 @@
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>50</v>
@@ -4373,7 +4371,7 @@
         <v>50</v>
       </c>
       <c r="P49" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q49" s="5">
         <v>1</v>
@@ -4400,7 +4398,7 @@
       <c r="AC49" s="5"/>
       <c r="AD49" s="5"/>
       <c r="AE49" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AF49" s="5"/>
       <c r="AG49" s="5"/>
@@ -4411,19 +4409,19 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -4434,7 +4432,7 @@
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>50</v>
@@ -4444,7 +4442,7 @@
         <v>60</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q50" s="5">
         <v>1</v>
@@ -4471,7 +4469,7 @@
       <c r="AC50" s="5"/>
       <c r="AD50" s="5"/>
       <c r="AE50" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AF50" s="5"/>
       <c r="AG50" s="5"/>
@@ -4482,22 +4480,22 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
     </row>
-    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -4507,7 +4505,7 @@
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>50</v>
@@ -4517,7 +4515,7 @@
         <v>250</v>
       </c>
       <c r="P51" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q51" s="5">
         <v>30</v>
@@ -4526,7 +4524,7 @@
         <v>52</v>
       </c>
       <c r="S51" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T51" s="5">
         <v>1</v>
@@ -4553,22 +4551,22 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
     </row>
-    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4578,7 +4576,7 @@
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M52" s="5" t="s">
         <v>50</v>
@@ -4588,7 +4586,7 @@
         <v>450</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q52" s="5">
         <v>30</v>
@@ -4597,7 +4595,7 @@
         <v>52</v>
       </c>
       <c r="S52" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T52" s="5">
         <v>1</v>
@@ -4624,22 +4622,22 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
     </row>
-    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4649,7 +4647,7 @@
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M53" s="5" t="s">
         <v>50</v>
@@ -4659,7 +4657,7 @@
         <v>750</v>
       </c>
       <c r="P53" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q53" s="5">
         <v>30</v>
@@ -4668,7 +4666,7 @@
         <v>52</v>
       </c>
       <c r="S53" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T53" s="5">
         <v>1</v>
@@ -4695,22 +4693,22 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
     </row>
-    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4728,7 +4726,7 @@
         <v>29.444400000000002</v>
       </c>
       <c r="P54" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="Q54" s="5">
         <v>1</v>
@@ -4755,7 +4753,7 @@
       <c r="AC54" s="5"/>
       <c r="AD54" s="5"/>
       <c r="AE54" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="AF54" s="5"/>
       <c r="AG54" s="5"/>
@@ -4766,22 +4764,22 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
     </row>
-    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4799,7 +4797,7 @@
         <v>5</v>
       </c>
       <c r="P55" s="5" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="Q55" s="5">
         <v>30</v>
@@ -4808,7 +4806,7 @@
         <v>52</v>
       </c>
       <c r="S55" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T55" s="5">
         <v>1</v>
@@ -4835,22 +4833,22 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
     </row>
-    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4868,7 +4866,7 @@
         <v>5</v>
       </c>
       <c r="P56" s="5" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="Q56" s="5">
         <v>30</v>
@@ -4877,7 +4875,7 @@
         <v>52</v>
       </c>
       <c r="S56" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T56" s="5">
         <v>1</v>

--- a/inst/extdata/north_dakota_criteria_crosswalk.xlsx
+++ b/inst/extdata/north_dakota_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{EDAF4E98-0AFF-4481-BB14-569D81D84F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64E058DA-B1F8-4E5B-9A9C-32C4A1870563}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD734A6-B475-40BD-81BD-B7CAE40B5906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -323,9 +323,6 @@
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
-    <t>#/100mL</t>
-  </si>
-  <si>
     <t>geometric mean</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>Where the pH is equal to or greater than 7.0, and the hardness is equal to or greater than 50 mg/l as CaCO3 in the receiving water after mixing, the 87 ug/l chronic total recoverable aluminum criterion will not apply, and aluminum will be regulated based on compliance with the 750 ug/l acute total recoverable aluminum criterion.</t>
+  </si>
+  <si>
+    <t>CFU/100ML</t>
   </si>
 </sst>
 </file>
@@ -829,15 +829,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D75899-4D8D-4FC8-9793-6F1E23FF217F}">
   <dimension ref="A1:AP56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="5"/>
+    <col min="2" max="2" width="32.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -965,7 +965,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>42</v>
@@ -1035,7 +1035,7 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -1100,7 +1100,7 @@
         <v>63</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
@@ -1109,13 +1109,13 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>44</v>
@@ -1181,13 +1181,13 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>44</v>
@@ -1253,13 +1253,13 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>44</v>
@@ -1325,13 +1325,13 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>44</v>
@@ -1397,7 +1397,7 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>42</v>
@@ -1467,7 +1467,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>42</v>
@@ -1537,7 +1537,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>42</v>
@@ -1605,7 +1605,7 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>42</v>
@@ -1673,7 +1673,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>42</v>
@@ -1741,7 +1741,7 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>42</v>
@@ -1809,7 +1809,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>42</v>
@@ -1879,7 +1879,7 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -1949,7 +1949,7 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>42</v>
@@ -2019,7 +2019,7 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>42</v>
@@ -2089,7 +2089,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>42</v>
@@ -2159,7 +2159,7 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>42</v>
@@ -2229,7 +2229,7 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>42</v>
@@ -2299,7 +2299,7 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>42</v>
@@ -2369,7 +2369,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>42</v>
@@ -2439,7 +2439,7 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>42</v>
@@ -2509,7 +2509,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>42</v>
@@ -2579,7 +2579,7 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
@@ -2649,7 +2649,7 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>42</v>
@@ -2719,7 +2719,7 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>42</v>
@@ -2789,7 +2789,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>42</v>
@@ -2859,13 +2859,13 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>44</v>
@@ -2929,13 +2929,13 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>44</v>
@@ -2999,7 +2999,7 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
@@ -3065,13 +3065,13 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>86</v>
@@ -3131,13 +3131,13 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>44</v>
@@ -3199,7 +3199,7 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>42</v>
@@ -3265,7 +3265,7 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>42</v>
@@ -3331,13 +3331,13 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>69</v>
@@ -3397,13 +3397,13 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>86</v>
@@ -3428,7 +3428,7 @@
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
@@ -3437,7 +3437,7 @@
         <v>51</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T37" s="3">
         <v>10</v>
@@ -3449,13 +3449,13 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Z37" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA37" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="AA37" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3469,13 +3469,13 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>86</v>
@@ -3500,7 +3500,7 @@
         <v>409</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
@@ -3521,13 +3521,13 @@
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Z38" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA38" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="AA38" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -3541,19 +3541,19 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>49</v>
@@ -3576,16 +3576,16 @@
         <v>9</v>
       </c>
       <c r="P39" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>1</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="Q39" s="3">
-        <v>1</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
@@ -3611,19 +3611,19 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -3646,16 +3646,16 @@
         <v>9</v>
       </c>
       <c r="P40" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>1</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>1</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="T40" s="3">
         <v>1</v>
@@ -3681,19 +3681,19 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -3716,16 +3716,16 @@
         <v>9</v>
       </c>
       <c r="P41" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>1</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>1</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
@@ -3751,19 +3751,19 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>56</v>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>49</v>
@@ -3821,19 +3821,19 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
@@ -3889,19 +3889,19 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>49</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
@@ -3957,19 +3957,19 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -3990,7 +3990,7 @@
         <v>50</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
@@ -4025,19 +4025,19 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>49</v>
@@ -4058,7 +4058,7 @@
         <v>60</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
@@ -4093,19 +4093,19 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -4126,7 +4126,7 @@
         <v>50</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
@@ -4161,19 +4161,19 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>49</v>
@@ -4194,7 +4194,7 @@
         <v>60</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
@@ -4229,19 +4229,19 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>78</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -4262,7 +4262,7 @@
         <v>50</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
@@ -4297,19 +4297,19 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>78</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>49</v>
@@ -4330,7 +4330,7 @@
         <v>60</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
@@ -4365,19 +4365,19 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>56</v>
@@ -4435,19 +4435,19 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>56</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>49</v>
@@ -4505,19 +4505,19 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>56</v>
@@ -4575,19 +4575,19 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>56</v>
@@ -4608,7 +4608,7 @@
         <v>29.444400000000002</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
@@ -4638,7 +4638,7 @@
         <v>63</v>
       </c>
       <c r="AF54" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG54" s="3"/>
       <c r="AH54" s="3"/>
@@ -4647,19 +4647,19 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>56</v>
@@ -4680,7 +4680,7 @@
         <v>5</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
@@ -4715,19 +4715,19 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>56</v>
@@ -4748,7 +4748,7 @@
         <v>5</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q56" s="3">
         <v>30</v>

--- a/inst/extdata/north_dakota_criteria_crosswalk.xlsx
+++ b/inst/extdata/north_dakota_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD734A6-B475-40BD-81BD-B7CAE40B5906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0191A328-8CF7-4BB2-B4FA-16E04F0012EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>EquationType</t>
   </si>
   <si>
-    <t>Equation</t>
-  </si>
-  <si>
     <t>hardness_param_1</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>CFU/100ML</t>
+  </si>
+  <si>
+    <t>EquationFormula</t>
   </si>
 </sst>
 </file>
@@ -829,15 +829,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D75899-4D8D-4FC8-9793-6F1E23FF217F}">
   <dimension ref="A1:AP56"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.26953125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.1796875" style="5"/>
+    <col min="2" max="2" width="32.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -932,90 +932,90 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>750</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1035,57 +1035,57 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>87</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q3" s="3">
         <v>1</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3">
+        <v>1</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T3" s="3">
-        <v>1</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1097,10 +1097,10 @@
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
@@ -1109,55 +1109,55 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1169,10 +1169,10 @@
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
@@ -1181,55 +1181,55 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q5" s="3">
-        <v>1</v>
-      </c>
-      <c r="R5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1241,10 +1241,10 @@
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
@@ -1253,55 +1253,55 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q6" s="3">
         <v>30</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1313,10 +1313,10 @@
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
@@ -1325,55 +1325,55 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q7" s="3">
         <v>4</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1385,10 +1385,10 @@
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
@@ -1397,57 +1397,57 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3">
         <v>5.6</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q8" s="3">
         <v>1</v>
       </c>
       <c r="R8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1467,57 +1467,57 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3">
         <v>640</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q9" s="3">
         <v>1</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1537,55 +1537,55 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3">
         <v>1</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T10" s="3">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1605,55 +1605,55 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>0.75</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q11" s="3">
         <v>30</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1673,55 +1673,55 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>0.75</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T12" s="3">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1741,55 +1741,55 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>0.75</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q13" s="3">
         <v>30</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1809,57 +1809,57 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3">
         <v>100</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q14" s="3">
         <v>30</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1879,57 +1879,57 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3">
         <v>175</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q15" s="3">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -1949,57 +1949,57 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>250</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q16" s="3">
         <v>30</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T16" s="3">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2019,57 +2019,57 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>100</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q17" s="3">
         <v>30</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2089,57 +2089,57 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>175</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2159,57 +2159,57 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>250</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q19" s="3">
         <v>30</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T19" s="3">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2229,57 +2229,57 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q20" s="3">
         <v>30</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T20" s="3">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2299,57 +2299,57 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3">
         <v>175</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q21" s="3">
         <v>30</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2369,57 +2369,57 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3">
         <v>250</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q22" s="3">
         <v>30</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2439,57 +2439,57 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>100</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q23" s="3">
         <v>30</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2509,57 +2509,57 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>175</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2579,57 +2579,57 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>250</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2649,57 +2649,57 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>100</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2719,57 +2719,57 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>175</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q27" s="3">
         <v>30</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2789,57 +2789,57 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>250</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2859,57 +2859,57 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>1.9E-2</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -2929,57 +2929,57 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -2999,53 +2999,53 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>15</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
       </c>
       <c r="R31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S31" s="3" t="s">
+      <c r="T31" s="3">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3065,53 +3065,53 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>8</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
       </c>
       <c r="R32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S32" s="3" t="s">
+      <c r="T32" s="3">
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3131,55 +3131,55 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N33" s="3">
         <v>5</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q33" s="3">
         <v>1</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T33" s="3">
         <v>10</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3199,53 +3199,53 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>1</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T34" s="3">
         <v>10</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3265,53 +3265,53 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>1</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S35" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T35" s="3">
         <v>10</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3331,53 +3331,53 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>1</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S36" s="3" t="s">
+      <c r="T36" s="3">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T36" s="3">
-        <v>1</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3397,65 +3397,65 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T37" s="3">
         <v>10</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z37" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA37" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="AA37" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3469,65 +3469,65 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>409</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
       </c>
       <c r="R38" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T38" s="3">
         <v>10</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z38" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA38" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="AA38" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -3541,33 +3541,33 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N39" s="3">
         <v>6.5</v>
@@ -3576,22 +3576,22 @@
         <v>9</v>
       </c>
       <c r="P39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>1</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q39" s="3">
-        <v>1</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3611,33 +3611,33 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N40" s="3">
         <v>6</v>
@@ -3646,22 +3646,22 @@
         <v>9</v>
       </c>
       <c r="P40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>1</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q40" s="3">
-        <v>1</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3681,33 +3681,33 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N41" s="3">
         <v>6</v>
@@ -3716,22 +3716,22 @@
         <v>9</v>
       </c>
       <c r="P41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>1</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q41" s="3">
-        <v>1</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3751,57 +3751,57 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>0.3</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3821,55 +3821,55 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>50</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
       </c>
       <c r="R43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S43" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S43" s="3" t="s">
+      <c r="T43" s="3">
+        <v>1</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -3889,55 +3889,55 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>60</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
       </c>
       <c r="R44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S44" s="3" t="s">
+      <c r="T44" s="3">
+        <v>1</v>
+      </c>
+      <c r="U44" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -3957,55 +3957,55 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>50</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S45" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S45" s="3" t="s">
+      <c r="T45" s="3">
+        <v>1</v>
+      </c>
+      <c r="U45" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4025,55 +4025,55 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>60</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S46" s="3" t="s">
+      <c r="T46" s="3">
+        <v>1</v>
+      </c>
+      <c r="U46" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T46" s="3">
-        <v>1</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4093,55 +4093,55 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>50</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S47" s="3" t="s">
+      <c r="T47" s="3">
+        <v>1</v>
+      </c>
+      <c r="U47" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4161,55 +4161,55 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>60</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S48" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S48" s="3" t="s">
+      <c r="T48" s="3">
+        <v>1</v>
+      </c>
+      <c r="U48" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4229,55 +4229,55 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>50</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S49" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S49" s="3" t="s">
+      <c r="T49" s="3">
+        <v>1</v>
+      </c>
+      <c r="U49" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4297,55 +4297,55 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>60</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S50" s="3" t="s">
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4365,57 +4365,57 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="F51" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>250</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q51" s="3">
         <v>30</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T51" s="3">
         <v>1</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4435,57 +4435,57 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="F52" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>450</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4505,57 +4505,57 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="F53" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>750</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q53" s="3">
         <v>30</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4575,55 +4575,55 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="F54" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>29.444400000000002</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S54" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S54" s="3" t="s">
+      <c r="T54" s="3">
+        <v>1</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4635,10 +4635,10 @@
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
       <c r="AE54" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF54" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG54" s="3"/>
       <c r="AH54" s="3"/>
@@ -4647,55 +4647,55 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>5</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T55" s="3">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4715,55 +4715,55 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3">
         <v>5</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q56" s="3">
         <v>30</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>

--- a/inst/extdata/north_dakota_criteria_crosswalk.xlsx
+++ b/inst/extdata/north_dakota_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0191A328-8CF7-4BB2-B4FA-16E04F0012EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{0191A328-8CF7-4BB2-B4FA-16E04F0012EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AD62033-8A3C-430C-8B3F-22D5269563DA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="130">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -143,12 +143,6 @@
     <t>hardness_param_4</t>
   </si>
   <si>
-    <t>hardness_param_5</t>
-  </si>
-  <si>
-    <t>hardness_param_6</t>
-  </si>
-  <si>
     <t>pH_param_1</t>
   </si>
   <si>
@@ -221,24 +215,9 @@
     <t>n-samples in 3 years</t>
   </si>
   <si>
-    <t>Where Oncorynchus are present; See Table 1 in ND standards for equation</t>
-  </si>
-  <si>
-    <t>Additional Information</t>
-  </si>
-  <si>
-    <t>Where Oncorynchus are not present; See Table 1 in ND standards for equation</t>
-  </si>
-  <si>
-    <t>See Table 1 in ND standards for equation</t>
-  </si>
-  <si>
     <t>rolling arithmetic mean</t>
   </si>
   <si>
-    <t>See Table 1 in ND standards for equation; Should not be more than 2.5 times the criteria more than once in three years on average</t>
-  </si>
-  <si>
     <t>Antimony</t>
   </si>
   <si>
@@ -377,9 +356,6 @@
     <t>DEG C</t>
   </si>
   <si>
-    <t>Maximum increase shall not be greater than 5 deg F above natural background conditions</t>
-  </si>
-  <si>
     <t>RADIUM-226/228</t>
   </si>
   <si>
@@ -416,20 +392,47 @@
     <t>Sep 30</t>
   </si>
   <si>
-    <t>Where the pH is equal to or greater than 7.0, and the hardness is equal to or greater than 50 mg/l as CaCO3 in the receiving water after mixing, the 87 ug/l chronic total recoverable aluminum criterion will not apply, and aluminum will be regulated based on compliance with the 750 ug/l acute total recoverable aluminum criterion.</t>
-  </si>
-  <si>
     <t>CFU/100ML</t>
   </si>
   <si>
-    <t>EquationFormula</t>
+    <t>pHThreshold</t>
+  </si>
+  <si>
+    <t>pHDirection</t>
+  </si>
+  <si>
+    <t>TemperatureExtreme</t>
+  </si>
+  <si>
+    <t>pH_param_9</t>
+  </si>
+  <si>
+    <t>pH_param_8</t>
+  </si>
+  <si>
+    <t>pH_param_7</t>
+  </si>
+  <si>
+    <t>pH_param_6</t>
+  </si>
+  <si>
+    <t>pH_param_5</t>
+  </si>
+  <si>
+    <t>MinEqMagnitude</t>
+  </si>
+  <si>
+    <t>MaxEqMagnitude</t>
+  </si>
+  <si>
+    <t>Equation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,6 +459,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -477,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -492,6 +502,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -828,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D75899-4D8D-4FC8-9793-6F1E23FF217F}">
-  <dimension ref="A1:AP56"/>
+  <dimension ref="A1:AX56"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" style="5" bestFit="1" customWidth="1"/>
@@ -837,7 +850,7 @@
     <col min="4" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -932,90 +945,114 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AW1" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>750</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T2" s="3">
         <v>1</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1034,58 +1071,59 @@
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
-    </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM2" s="3"/>
+    </row>
+    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>87</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" s="3">
-        <v>1</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T3" s="3">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1096,68 +1134,65 @@
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
-      <c r="AE3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
-    </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM3" s="3"/>
+    </row>
+    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1168,68 +1203,65 @@
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
-      <c r="AE4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
-    </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM4" s="3"/>
+    </row>
+    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Q5" s="3">
-        <v>1</v>
-      </c>
-      <c r="R5" s="3" t="s">
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1240,68 +1272,65 @@
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
-      <c r="AE5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
-    </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM5" s="3"/>
+    </row>
+    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q6" s="3">
         <v>30</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T6" s="3">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1312,68 +1341,65 @@
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
-      <c r="AE6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF6" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
-    </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM6" s="3"/>
+    </row>
+    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="3">
         <v>4</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1384,70 +1410,67 @@
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
-      <c r="AE7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF7" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
-    </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM7" s="3"/>
+    </row>
+    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3">
         <v>5.6</v>
       </c>
       <c r="P8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="3">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T8" s="3">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1466,58 +1489,59 @@
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
-    </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM8" s="3"/>
+    </row>
+    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3">
         <v>640</v>
       </c>
       <c r="P9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T9" s="3">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1536,56 +1560,57 @@
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
-    </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM9" s="3"/>
+    </row>
+    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3">
         <v>1</v>
       </c>
       <c r="P10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Q10" s="3">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="T10" s="3">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1604,56 +1629,57 @@
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
-    </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM10" s="3"/>
+    </row>
+    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>0.75</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q11" s="3">
         <v>30</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1672,56 +1698,57 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM11" s="3"/>
+    </row>
+    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>0.75</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T12" s="3">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1740,56 +1767,57 @@
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
-    </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM12" s="3"/>
+    </row>
+    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>0.75</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q13" s="3">
         <v>30</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1808,58 +1836,59 @@
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
-    </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM13" s="3"/>
+    </row>
+    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3">
         <v>100</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q14" s="3">
         <v>30</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1878,58 +1907,59 @@
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM14" s="3"/>
+    </row>
+    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3">
         <v>175</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q15" s="3">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -1948,58 +1978,59 @@
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM15" s="3"/>
+    </row>
+    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>250</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q16" s="3">
         <v>30</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T16" s="3">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2018,58 +2049,59 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
-    </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM16" s="3"/>
+    </row>
+    <row r="17" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>100</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q17" s="3">
         <v>30</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2088,58 +2120,59 @@
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
-    </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM17" s="3"/>
+    </row>
+    <row r="18" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>175</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2158,58 +2191,59 @@
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
-    </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM18" s="3"/>
+    </row>
+    <row r="19" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>250</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q19" s="3">
         <v>30</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T19" s="3">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2228,58 +2262,59 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
-    </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM19" s="3"/>
+    </row>
+    <row r="20" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q20" s="3">
         <v>30</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T20" s="3">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2298,58 +2333,59 @@
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
-    </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM20" s="3"/>
+    </row>
+    <row r="21" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3">
         <v>175</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q21" s="3">
         <v>30</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2368,58 +2404,59 @@
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
-    </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM21" s="3"/>
+    </row>
+    <row r="22" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3">
         <v>250</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q22" s="3">
         <v>30</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2438,58 +2475,59 @@
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
-    </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM22" s="3"/>
+    </row>
+    <row r="23" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>100</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q23" s="3">
         <v>30</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2508,58 +2546,59 @@
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
-    </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM23" s="3"/>
+    </row>
+    <row r="24" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>175</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2578,58 +2617,59 @@
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
-    </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM24" s="3"/>
+    </row>
+    <row r="25" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>250</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2648,58 +2688,59 @@
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
-    </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM25" s="3"/>
+    </row>
+    <row r="26" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>100</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2718,58 +2759,59 @@
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
-    </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM26" s="3"/>
+    </row>
+    <row r="27" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>175</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q27" s="3">
         <v>30</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2788,58 +2830,59 @@
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
-    </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM27" s="3"/>
+    </row>
+    <row r="28" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>250</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2858,58 +2901,59 @@
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
-    </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM28" s="3"/>
+    </row>
+    <row r="29" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>1.9E-2</v>
       </c>
       <c r="P29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Q29" s="3">
-        <v>1</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -2928,58 +2972,59 @@
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
-    </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM29" s="3"/>
+    </row>
+    <row r="30" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -2998,54 +3043,55 @@
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
-    </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM30" s="3"/>
+    </row>
+    <row r="31" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>15</v>
       </c>
       <c r="P31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>1</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q31" s="3">
-        <v>1</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3064,54 +3110,55 @@
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
-    </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM31" s="3"/>
+    </row>
+    <row r="32" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>8</v>
       </c>
       <c r="P32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>1</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q32" s="3">
-        <v>1</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T32" s="3">
         <v>1</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3130,56 +3177,57 @@
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
-    </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM32" s="3"/>
+    </row>
+    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N33" s="3">
         <v>5</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q33" s="3">
         <v>1</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="T33" s="3">
         <v>10</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3198,54 +3246,55 @@
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
-    </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM33" s="3"/>
+    </row>
+    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>1</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T34" s="3">
         <v>10</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3264,54 +3313,55 @@
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
-    </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM34" s="3"/>
+    </row>
+    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>1</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T35" s="3">
         <v>10</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3330,54 +3380,55 @@
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
-    </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM35" s="3"/>
+    </row>
+    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>1</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T36" s="3">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3396,66 +3447,67 @@
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
-    </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM36" s="3"/>
+    </row>
+    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="T37" s="3">
         <v>10</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="Z37" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="AA37" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3468,66 +3520,67 @@
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
-    </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM37" s="3"/>
+    </row>
+    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>409</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T38" s="3">
         <v>10</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="Z38" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="AA38" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -3540,34 +3593,35 @@
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
-    </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM38" s="3"/>
+    </row>
+    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N39" s="3">
         <v>6.5</v>
@@ -3576,22 +3630,22 @@
         <v>9</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="Q39" s="3">
         <v>1</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3610,34 +3664,35 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
-    </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM39" s="3"/>
+    </row>
+    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N40" s="3">
         <v>6</v>
@@ -3646,22 +3701,22 @@
         <v>9</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3680,34 +3735,35 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
-    </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM40" s="3"/>
+    </row>
+    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N41" s="3">
         <v>6</v>
@@ -3716,22 +3772,22 @@
         <v>9</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3750,58 +3806,59 @@
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
-    </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM41" s="3"/>
+    </row>
+    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>0.3</v>
       </c>
       <c r="P42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>1</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Q42" s="3">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3820,56 +3877,57 @@
       <c r="AJ42" s="3"/>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
-    </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM42" s="3"/>
+    </row>
+    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>50</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -3888,56 +3946,57 @@
       <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
-    </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM43" s="3"/>
+    </row>
+    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>60</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T44" s="3">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -3956,56 +4015,57 @@
       <c r="AJ44" s="3"/>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
-    </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM44" s="3"/>
+    </row>
+    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>50</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4024,56 +4084,57 @@
       <c r="AJ45" s="3"/>
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
-    </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM45" s="3"/>
+    </row>
+    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>60</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4092,56 +4153,57 @@
       <c r="AJ46" s="3"/>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
-    </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM46" s="3"/>
+    </row>
+    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>50</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4160,56 +4222,57 @@
       <c r="AJ47" s="3"/>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
-    </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM47" s="3"/>
+    </row>
+    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>60</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T48" s="3">
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4228,56 +4291,57 @@
       <c r="AJ48" s="3"/>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
-    </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM48" s="3"/>
+    </row>
+    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>50</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4296,56 +4360,57 @@
       <c r="AJ49" s="3"/>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
-    </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM49" s="3"/>
+    </row>
+    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>60</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4364,58 +4429,59 @@
       <c r="AJ50" s="3"/>
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
-    </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM50" s="3"/>
+    </row>
+    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>250</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q51" s="3">
         <v>30</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T51" s="3">
         <v>1</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4434,58 +4500,59 @@
       <c r="AJ51" s="3"/>
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
-    </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM51" s="3"/>
+    </row>
+    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>450</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4504,58 +4571,59 @@
       <c r="AJ52" s="3"/>
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
-    </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM52" s="3"/>
+    </row>
+    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>750</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q53" s="3">
         <v>30</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4574,56 +4642,57 @@
       <c r="AJ53" s="3"/>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
-    </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM53" s="3"/>
+    </row>
+    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>29.444400000000002</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T54" s="3">
         <v>1</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4634,68 +4703,65 @@
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
-      <c r="AE54" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF54" s="3" t="s">
-        <v>113</v>
-      </c>
+      <c r="AE54" s="3"/>
+      <c r="AF54" s="3"/>
       <c r="AG54" s="3"/>
       <c r="AH54" s="3"/>
       <c r="AI54" s="3"/>
       <c r="AJ54" s="3"/>
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
-    </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM54" s="3"/>
+    </row>
+    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>5</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T55" s="3">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4714,56 +4780,57 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
-    </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM55" s="3"/>
+    </row>
+    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3">
         <v>5</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="Q56" s="3">
         <v>30</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4782,6 +4849,7 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inst/extdata/north_dakota_criteria_crosswalk.xlsx
+++ b/inst/extdata/north_dakota_criteria_crosswalk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{0191A328-8CF7-4BB2-B4FA-16E04F0012EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AD62033-8A3C-430C-8B3F-22D5269563DA}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{0191A328-8CF7-4BB2-B4FA-16E04F0012EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA053EB6-0791-4933-BBD1-F9CF7059F842}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="133">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -401,9 +401,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>pH_param_9</t>
   </si>
   <si>
@@ -426,6 +423,18 @@
   </si>
   <si>
     <t>Equation</t>
+  </si>
+  <si>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
   </si>
 </sst>
 </file>
@@ -841,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D75899-4D8D-4FC8-9793-6F1E23FF217F}">
-  <dimension ref="A1:AX56"/>
+  <dimension ref="A1:BA56"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" style="5" bestFit="1" customWidth="1"/>
@@ -850,7 +859,7 @@
     <col min="4" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -945,7 +954,7 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>119</v>
@@ -966,7 +975,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -981,28 +990,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ1" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="AS1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AW1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="AX1" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1073,7 +1091,7 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1144,7 +1162,7 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1213,7 +1231,7 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
     </row>
-    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1282,7 +1300,7 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
     </row>
-    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1351,7 +1369,7 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
     </row>
-    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1420,7 +1438,7 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
     </row>
-    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1491,7 +1509,7 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
     </row>
-    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1562,7 +1580,7 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
     </row>
-    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1631,7 +1649,7 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
     </row>
-    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -1700,7 +1718,7 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -1769,7 +1787,7 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -1838,7 +1856,7 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
     </row>
-    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -1909,7 +1927,7 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
     </row>
-    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -1980,7 +1998,7 @@
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
     </row>
-    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>

--- a/inst/extdata/north_dakota_criteria_crosswalk.xlsx
+++ b/inst/extdata/north_dakota_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{0191A328-8CF7-4BB2-B4FA-16E04F0012EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA053EB6-0791-4933-BBD1-F9CF7059F842}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{0191A328-8CF7-4BB2-B4FA-16E04F0012EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE1E0AD8-4A15-4010-925D-8EAC44B7FE11}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="132">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -101,18 +101,12 @@
     <t>FreqMethod</t>
   </si>
   <si>
-    <t>AssessPeriod</t>
-  </si>
-  <si>
     <t>AssessPeriodStartDate</t>
   </si>
   <si>
     <t>AssessPeriodEndDate</t>
   </si>
   <si>
-    <t>Season</t>
-  </si>
-  <si>
     <t>SeasonStartDate</t>
   </si>
   <si>
@@ -302,9 +296,6 @@
     <t>geometric mean</t>
   </si>
   <si>
-    <t>May 1 - Sep 30</t>
-  </si>
-  <si>
     <t>pH</t>
   </si>
   <si>
@@ -435,6 +426,12 @@
   </si>
   <si>
     <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Links</t>
   </si>
 </sst>
 </file>
@@ -851,15 +848,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D75899-4D8D-4FC8-9793-6F1E23FF217F}">
   <dimension ref="A1:BA56"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="5"/>
+    <col min="2" max="2" width="32.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -945,139 +942,139 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AX1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AZ1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA1" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="AT1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AZ1" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="BA1" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>750</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
@@ -1091,64 +1088,64 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>87</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="3">
-        <v>1</v>
-      </c>
-      <c r="R3" s="3" t="s">
+      <c r="T3" s="3">
+        <v>1</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T3" s="3">
-        <v>1</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -1162,62 +1159,62 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -1231,62 +1228,62 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
     </row>
-    <row r="5" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Q5" s="3">
-        <v>1</v>
-      </c>
-      <c r="R5" s="3" t="s">
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -1300,62 +1297,62 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
     </row>
-    <row r="6" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q6" s="3">
         <v>30</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T6" s="3">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -1369,62 +1366,62 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
     </row>
-    <row r="7" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q7" s="3">
         <v>4</v>
       </c>
       <c r="R7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1</v>
+      </c>
+      <c r="U7" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T7" s="3">
-        <v>1</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -1438,64 +1435,64 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
     </row>
-    <row r="8" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3">
         <v>5.6</v>
       </c>
       <c r="P8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="3">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3" t="s">
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -1509,64 +1506,64 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
     </row>
-    <row r="9" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3">
         <v>640</v>
       </c>
       <c r="P9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -1580,62 +1577,62 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
     </row>
-    <row r="10" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3">
         <v>1</v>
       </c>
       <c r="P10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Q10" s="3">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3" t="s">
+      <c r="T10" s="3">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -1649,62 +1646,62 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
     </row>
-    <row r="11" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>0.75</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="3">
         <v>30</v>
       </c>
       <c r="R11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T11" s="3">
+        <v>1</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T11" s="3">
-        <v>1</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -1718,62 +1715,62 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="F12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>0.75</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -1787,62 +1784,62 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>0.75</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q13" s="3">
         <v>30</v>
       </c>
       <c r="R13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T13" s="3">
+        <v>1</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -1856,64 +1853,64 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
     </row>
-    <row r="14" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3">
         <v>100</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q14" s="3">
         <v>30</v>
       </c>
       <c r="R14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T14" s="3">
+        <v>1</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -1927,64 +1924,64 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
     </row>
-    <row r="15" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3">
         <v>175</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q15" s="3">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -1998,64 +1995,64 @@
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
     </row>
-    <row r="16" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>250</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q16" s="3">
         <v>30</v>
       </c>
       <c r="R16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T16" s="3">
+        <v>1</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T16" s="3">
-        <v>1</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2069,64 +2066,64 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>100</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q17" s="3">
         <v>30</v>
       </c>
       <c r="R17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -2140,64 +2137,64 @@
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
     </row>
-    <row r="18" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>175</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2211,64 +2208,64 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
     </row>
-    <row r="19" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>250</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q19" s="3">
         <v>30</v>
       </c>
       <c r="R19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T19" s="3">
-        <v>1</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -2282,64 +2279,64 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q20" s="3">
         <v>30</v>
       </c>
       <c r="R20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -2353,64 +2350,64 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
     </row>
-    <row r="21" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3">
         <v>175</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q21" s="3">
         <v>30</v>
       </c>
       <c r="R21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T21" s="3">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T21" s="3">
-        <v>1</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
@@ -2424,64 +2421,64 @@
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
     </row>
-    <row r="22" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3">
         <v>250</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q22" s="3">
         <v>30</v>
       </c>
       <c r="R22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T22" s="3">
+        <v>1</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
@@ -2495,64 +2492,64 @@
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
     </row>
-    <row r="23" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>100</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q23" s="3">
         <v>30</v>
       </c>
       <c r="R23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T23" s="3">
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -2566,64 +2563,64 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>175</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -2637,64 +2634,64 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>250</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T25" s="3">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T25" s="3">
-        <v>1</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -2708,64 +2705,64 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>100</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -2779,64 +2776,64 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>175</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q27" s="3">
         <v>30</v>
       </c>
       <c r="R27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1</v>
+      </c>
+      <c r="U27" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -2850,64 +2847,64 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
     </row>
-    <row r="28" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>250</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T28" s="3">
+        <v>1</v>
+      </c>
+      <c r="U28" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T28" s="3">
-        <v>1</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -2921,64 +2918,64 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
     </row>
-    <row r="29" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>1.9E-2</v>
       </c>
       <c r="P29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Q29" s="3">
-        <v>1</v>
-      </c>
-      <c r="R29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T29" s="3">
-        <v>1</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -2992,64 +2989,64 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
     </row>
-    <row r="30" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T30" s="3">
+        <v>1</v>
+      </c>
+      <c r="U30" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T30" s="3">
-        <v>1</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -3063,60 +3060,60 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
     </row>
-    <row r="31" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>15</v>
       </c>
       <c r="P31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>1</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q31" s="3">
-        <v>1</v>
-      </c>
-      <c r="R31" s="3" t="s">
+      <c r="T31" s="3">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
@@ -3130,60 +3127,60 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
     </row>
-    <row r="32" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>8</v>
       </c>
       <c r="P32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>1</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q32" s="3">
-        <v>1</v>
-      </c>
-      <c r="R32" s="3" t="s">
+      <c r="T32" s="3">
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -3197,62 +3194,62 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
     </row>
-    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N33" s="3">
         <v>5</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q33" s="3">
         <v>1</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T33" s="3">
         <v>10</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -3266,60 +3263,60 @@
       <c r="AL33" s="3"/>
       <c r="AM33" s="3"/>
     </row>
-    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>1</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T34" s="3">
         <v>10</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
@@ -3333,60 +3330,60 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
     </row>
-    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>1</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T35" s="3">
         <v>10</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3400,60 +3397,60 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>1</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T36" s="3">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T36" s="3">
-        <v>1</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -3467,66 +3464,64 @@
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="T37" s="3">
         <v>10</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z37" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA37" s="4" t="s">
-        <v>117</v>
-      </c>
+      <c r="X37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y37" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -3540,66 +3535,64 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>409</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T38" s="3">
         <v>10</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z38" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA38" s="4" t="s">
-        <v>117</v>
-      </c>
+      <c r="X38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y38" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
@@ -3613,33 +3606,33 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N39" s="3">
         <v>6.5</v>
@@ -3648,29 +3641,29 @@
         <v>9</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q39" s="3">
         <v>1</v>
       </c>
       <c r="R39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T39" s="3">
+        <v>1</v>
+      </c>
+      <c r="U39" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="T39" s="3">
-        <v>1</v>
-      </c>
-      <c r="U39" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
@@ -3684,33 +3677,33 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N40" s="3">
         <v>6</v>
@@ -3719,29 +3712,29 @@
         <v>9</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
       </c>
       <c r="R40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T40" s="3">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="T40" s="3">
-        <v>1</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
@@ -3755,33 +3748,33 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N41" s="3">
         <v>6</v>
@@ -3790,29 +3783,29 @@
         <v>9</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
       </c>
       <c r="R41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T41" s="3">
+        <v>1</v>
+      </c>
+      <c r="U41" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="T41" s="3">
-        <v>1</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
@@ -3826,64 +3819,64 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>0.3</v>
       </c>
       <c r="P42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>1</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Q42" s="3">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3" t="s">
+      <c r="T42" s="3">
+        <v>1</v>
+      </c>
+      <c r="U42" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T42" s="3">
-        <v>1</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
@@ -3897,62 +3890,62 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>50</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
       </c>
       <c r="R43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T43" s="3">
+        <v>1</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
@@ -3966,62 +3959,62 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>60</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
       </c>
       <c r="R44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T44" s="3">
+        <v>1</v>
+      </c>
+      <c r="U44" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
@@ -4035,62 +4028,62 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>50</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T45" s="3">
+        <v>1</v>
+      </c>
+      <c r="U45" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
@@ -4104,62 +4097,62 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>60</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T46" s="3">
+        <v>1</v>
+      </c>
+      <c r="U46" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T46" s="3">
-        <v>1</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="4"/>
-      <c r="AA46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -4173,62 +4166,62 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>50</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T47" s="3">
+        <v>1</v>
+      </c>
+      <c r="U47" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
@@ -4242,62 +4235,62 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>60</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T48" s="3">
+        <v>1</v>
+      </c>
+      <c r="U48" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -4311,62 +4304,62 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>50</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T49" s="3">
+        <v>1</v>
+      </c>
+      <c r="U49" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
@@ -4380,62 +4373,62 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>60</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
@@ -4449,64 +4442,64 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>250</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q51" s="3">
         <v>30</v>
       </c>
       <c r="R51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T51" s="3">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T51" s="3">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
       <c r="AD51" s="3"/>
@@ -4520,64 +4513,64 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>450</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T52" s="3">
+        <v>1</v>
+      </c>
+      <c r="U52" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
@@ -4591,64 +4584,64 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>750</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q53" s="3">
         <v>30</v>
       </c>
       <c r="R53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T53" s="3">
+        <v>1</v>
+      </c>
+      <c r="U53" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S53" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T53" s="3">
-        <v>1</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
@@ -4662,62 +4655,62 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>29.444400000000002</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T54" s="3">
+        <v>1</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
@@ -4731,62 +4724,62 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>5</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T55" s="3">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T55" s="3">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
@@ -4800,62 +4793,62 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3">
         <v>5</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q56" s="3">
         <v>30</v>
       </c>
       <c r="R56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T56" s="3">
+        <v>1</v>
+      </c>
+      <c r="U56" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T56" s="3">
-        <v>1</v>
-      </c>
-      <c r="U56" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
